--- a/AAII_Financials/Yearly/CIB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CIB_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6390100</v>
+        <v>6922600</v>
       </c>
       <c r="E8" s="3">
-        <v>3864500</v>
+        <v>4186500</v>
       </c>
       <c r="F8" s="3">
-        <v>4086300</v>
+        <v>4426900</v>
       </c>
       <c r="G8" s="3">
-        <v>4215200</v>
+        <v>4566500</v>
       </c>
       <c r="H8" s="3">
-        <v>3873400</v>
+        <v>4196200</v>
       </c>
       <c r="I8" s="3">
-        <v>4021900</v>
+        <v>4357100</v>
       </c>
       <c r="J8" s="3">
-        <v>3780900</v>
+        <v>4095900</v>
       </c>
       <c r="K8" s="3">
         <v>2359900</v>
@@ -993,25 +993,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-227900</v>
+        <v>-246900</v>
       </c>
       <c r="E15" s="3">
-        <v>-205200</v>
+        <v>-222300</v>
       </c>
       <c r="F15" s="3">
-        <v>-176700</v>
+        <v>-191500</v>
       </c>
       <c r="G15" s="3">
-        <v>-162500</v>
+        <v>-176100</v>
       </c>
       <c r="H15" s="3">
-        <v>-111900</v>
+        <v>-121200</v>
       </c>
       <c r="I15" s="3">
-        <v>-103900</v>
+        <v>-112600</v>
       </c>
       <c r="J15" s="3">
-        <v>-115000</v>
+        <v>-124500</v>
       </c>
       <c r="K15" s="3">
         <v>-96800</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2936200</v>
+        <v>3180900</v>
       </c>
       <c r="E17" s="3">
-        <v>1625300</v>
+        <v>1760700</v>
       </c>
       <c r="F17" s="3">
-        <v>3213500</v>
+        <v>3481300</v>
       </c>
       <c r="G17" s="3">
-        <v>2301800</v>
+        <v>2493600</v>
       </c>
       <c r="H17" s="3">
+        <v>2474200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2522400</v>
+      </c>
+      <c r="J17" s="3">
         <v>2283900</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2328400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2108200</v>
       </c>
       <c r="K17" s="3">
         <v>1198200</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3453900</v>
+        <v>3741800</v>
       </c>
       <c r="E18" s="3">
-        <v>2239200</v>
+        <v>2425800</v>
       </c>
       <c r="F18" s="3">
-        <v>872900</v>
+        <v>945600</v>
       </c>
       <c r="G18" s="3">
-        <v>1913400</v>
+        <v>2072900</v>
       </c>
       <c r="H18" s="3">
-        <v>1589500</v>
+        <v>1722000</v>
       </c>
       <c r="I18" s="3">
-        <v>1693500</v>
+        <v>1834700</v>
       </c>
       <c r="J18" s="3">
-        <v>1672600</v>
+        <v>1812000</v>
       </c>
       <c r="K18" s="3">
         <v>1161800</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1115200</v>
+        <v>-1208100</v>
       </c>
       <c r="E20" s="3">
-        <v>-803000</v>
+        <v>-870000</v>
       </c>
       <c r="F20" s="3">
-        <v>-798800</v>
+        <v>-865300</v>
       </c>
       <c r="G20" s="3">
-        <v>-838800</v>
+        <v>-908700</v>
       </c>
       <c r="H20" s="3">
-        <v>-721700</v>
+        <v>-781800</v>
       </c>
       <c r="I20" s="3">
-        <v>-735300</v>
+        <v>-796500</v>
       </c>
       <c r="J20" s="3">
-        <v>-720200</v>
+        <v>-780300</v>
       </c>
       <c r="K20" s="3">
         <v>-482300</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2576100</v>
+        <v>2780500</v>
       </c>
       <c r="E21" s="3">
-        <v>1650000</v>
+        <v>1778200</v>
       </c>
       <c r="F21" s="3">
-        <v>258200</v>
+        <v>271700</v>
       </c>
       <c r="G21" s="3">
-        <v>1243900</v>
+        <v>1340200</v>
       </c>
       <c r="H21" s="3">
-        <v>984800</v>
+        <v>1061700</v>
       </c>
       <c r="I21" s="3">
-        <v>1066500</v>
+        <v>1150700</v>
       </c>
       <c r="J21" s="3">
-        <v>1073100</v>
+        <v>1157300</v>
       </c>
       <c r="K21" s="3">
         <v>780600</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2338700</v>
+        <v>2533600</v>
       </c>
       <c r="E23" s="3">
-        <v>1436200</v>
+        <v>1555800</v>
       </c>
       <c r="F23" s="3">
-        <v>74100</v>
+        <v>80300</v>
       </c>
       <c r="G23" s="3">
-        <v>1074600</v>
+        <v>1164200</v>
       </c>
       <c r="H23" s="3">
-        <v>867800</v>
+        <v>940100</v>
       </c>
       <c r="I23" s="3">
-        <v>958300</v>
+        <v>1038100</v>
       </c>
       <c r="J23" s="3">
-        <v>952400</v>
+        <v>1031800</v>
       </c>
       <c r="K23" s="3">
         <v>679500</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>659600</v>
+        <v>714600</v>
       </c>
       <c r="E24" s="3">
-        <v>426300</v>
+        <v>461800</v>
       </c>
       <c r="F24" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="G24" s="3">
-        <v>303100</v>
+        <v>328400</v>
       </c>
       <c r="H24" s="3">
-        <v>199100</v>
+        <v>215700</v>
       </c>
       <c r="I24" s="3">
-        <v>297300</v>
+        <v>322000</v>
       </c>
       <c r="J24" s="3">
-        <v>282400</v>
+        <v>306000</v>
       </c>
       <c r="K24" s="3">
         <v>136300</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1679100</v>
+        <v>1819100</v>
       </c>
       <c r="E26" s="3">
-        <v>1009900</v>
+        <v>1094000</v>
       </c>
       <c r="F26" s="3">
-        <v>75700</v>
+        <v>82000</v>
       </c>
       <c r="G26" s="3">
-        <v>771500</v>
+        <v>835800</v>
       </c>
       <c r="H26" s="3">
-        <v>668700</v>
+        <v>724500</v>
       </c>
       <c r="I26" s="3">
-        <v>661000</v>
+        <v>716100</v>
       </c>
       <c r="J26" s="3">
-        <v>669900</v>
+        <v>725800</v>
       </c>
       <c r="K26" s="3">
         <v>543100</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1628000</v>
+        <v>1763700</v>
       </c>
       <c r="E27" s="3">
-        <v>980800</v>
+        <v>1062600</v>
       </c>
       <c r="F27" s="3">
-        <v>66200</v>
+        <v>71800</v>
       </c>
       <c r="G27" s="3">
-        <v>748200</v>
+        <v>810500</v>
       </c>
       <c r="H27" s="3">
-        <v>638100</v>
+        <v>691300</v>
       </c>
       <c r="I27" s="3">
-        <v>627600</v>
+        <v>679900</v>
       </c>
       <c r="J27" s="3">
-        <v>648400</v>
+        <v>702500</v>
       </c>
       <c r="K27" s="3">
         <v>524200</v>
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="J29" s="3">
-        <v>39200</v>
+        <v>42500</v>
       </c>
       <c r="K29" s="3">
         <v>4700</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1115200</v>
+        <v>1208100</v>
       </c>
       <c r="E32" s="3">
-        <v>803000</v>
+        <v>870000</v>
       </c>
       <c r="F32" s="3">
-        <v>798800</v>
+        <v>865300</v>
       </c>
       <c r="G32" s="3">
-        <v>838800</v>
+        <v>908700</v>
       </c>
       <c r="H32" s="3">
-        <v>721700</v>
+        <v>781800</v>
       </c>
       <c r="I32" s="3">
-        <v>735300</v>
+        <v>796500</v>
       </c>
       <c r="J32" s="3">
-        <v>720200</v>
+        <v>780300</v>
       </c>
       <c r="K32" s="3">
         <v>482300</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1628000</v>
+        <v>1763700</v>
       </c>
       <c r="E33" s="3">
-        <v>980800</v>
+        <v>1062600</v>
       </c>
       <c r="F33" s="3">
-        <v>66200</v>
+        <v>71800</v>
       </c>
       <c r="G33" s="3">
-        <v>748200</v>
+        <v>810500</v>
       </c>
       <c r="H33" s="3">
-        <v>638100</v>
+        <v>691300</v>
       </c>
       <c r="I33" s="3">
-        <v>627600</v>
+        <v>679900</v>
       </c>
       <c r="J33" s="3">
-        <v>687700</v>
+        <v>745000</v>
       </c>
       <c r="K33" s="3">
         <v>529000</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1628000</v>
+        <v>1763700</v>
       </c>
       <c r="E35" s="3">
-        <v>980800</v>
+        <v>1062600</v>
       </c>
       <c r="F35" s="3">
-        <v>66200</v>
+        <v>71800</v>
       </c>
       <c r="G35" s="3">
-        <v>748200</v>
+        <v>810500</v>
       </c>
       <c r="H35" s="3">
-        <v>638100</v>
+        <v>691300</v>
       </c>
       <c r="I35" s="3">
-        <v>627600</v>
+        <v>679900</v>
       </c>
       <c r="J35" s="3">
-        <v>687700</v>
+        <v>745000</v>
       </c>
       <c r="K35" s="3">
         <v>529000</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5933100</v>
+        <v>6427500</v>
       </c>
       <c r="E41" s="3">
-        <v>5555400</v>
+        <v>6018400</v>
       </c>
       <c r="F41" s="3">
-        <v>4844400</v>
+        <v>5248100</v>
       </c>
       <c r="G41" s="3">
-        <v>4381500</v>
+        <v>4746600</v>
       </c>
       <c r="H41" s="3">
-        <v>3799900</v>
+        <v>4116600</v>
       </c>
       <c r="I41" s="3">
-        <v>3725500</v>
+        <v>4036000</v>
       </c>
       <c r="J41" s="3">
-        <v>3892100</v>
+        <v>4216400</v>
       </c>
       <c r="K41" s="3">
         <v>3002000</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4370800</v>
+        <v>4735000</v>
       </c>
       <c r="E42" s="3">
-        <v>2280900</v>
+        <v>2471000</v>
       </c>
       <c r="F42" s="3">
-        <v>2591400</v>
+        <v>2807400</v>
       </c>
       <c r="G42" s="3">
-        <v>2771300</v>
+        <v>3002200</v>
       </c>
       <c r="H42" s="3">
-        <v>2078000</v>
+        <v>2251100</v>
       </c>
       <c r="I42" s="3">
-        <v>1836600</v>
+        <v>1989700</v>
       </c>
       <c r="J42" s="3">
-        <v>2188600</v>
+        <v>2371000</v>
       </c>
       <c r="K42" s="3">
         <v>2133100</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>699800</v>
+        <v>758100</v>
       </c>
       <c r="E47" s="3">
-        <v>652900</v>
+        <v>707300</v>
       </c>
       <c r="F47" s="3">
-        <v>601500</v>
+        <v>651600</v>
       </c>
       <c r="G47" s="3">
-        <v>568300</v>
+        <v>615600</v>
       </c>
       <c r="H47" s="3">
-        <v>515900</v>
+        <v>558900</v>
       </c>
       <c r="I47" s="3">
-        <v>375600</v>
+        <v>406900</v>
       </c>
       <c r="J47" s="3">
-        <v>311600</v>
+        <v>337500</v>
       </c>
       <c r="K47" s="3">
         <v>114800</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3011600</v>
+        <v>3262500</v>
       </c>
       <c r="E48" s="3">
-        <v>2382900</v>
+        <v>2581500</v>
       </c>
       <c r="F48" s="3">
-        <v>2112600</v>
+        <v>2288700</v>
       </c>
       <c r="G48" s="3">
-        <v>1803100</v>
+        <v>1953400</v>
       </c>
       <c r="H48" s="3">
-        <v>1224400</v>
+        <v>1326400</v>
       </c>
       <c r="I48" s="3">
-        <v>1148400</v>
+        <v>1244100</v>
       </c>
       <c r="J48" s="3">
-        <v>1127400</v>
+        <v>1221300</v>
       </c>
       <c r="K48" s="3">
         <v>996800</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2505400</v>
+        <v>2714200</v>
       </c>
       <c r="E49" s="3">
-        <v>2070900</v>
+        <v>2243500</v>
       </c>
       <c r="F49" s="3">
-        <v>1801800</v>
+        <v>1951900</v>
       </c>
       <c r="G49" s="3">
-        <v>1736000</v>
+        <v>1880700</v>
       </c>
       <c r="H49" s="3">
-        <v>1728400</v>
+        <v>1872500</v>
       </c>
       <c r="I49" s="3">
-        <v>1591500</v>
+        <v>1724200</v>
       </c>
       <c r="J49" s="3">
-        <v>1606600</v>
+        <v>1740400</v>
       </c>
       <c r="K49" s="3">
         <v>1489400</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>183500</v>
+        <v>198800</v>
       </c>
       <c r="E52" s="3">
-        <v>179100</v>
+        <v>194100</v>
       </c>
       <c r="F52" s="3">
-        <v>162100</v>
+        <v>175600</v>
       </c>
       <c r="G52" s="3">
-        <v>96200</v>
+        <v>104300</v>
       </c>
       <c r="H52" s="3">
-        <v>65100</v>
+        <v>70500</v>
       </c>
       <c r="I52" s="3">
-        <v>35700</v>
+        <v>38600</v>
       </c>
       <c r="J52" s="3">
-        <v>53500</v>
+        <v>57900</v>
       </c>
       <c r="K52" s="3">
         <v>35800</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>84675500</v>
+        <v>91731800</v>
       </c>
       <c r="E54" s="3">
-        <v>69565200</v>
+        <v>75362300</v>
       </c>
       <c r="F54" s="3">
-        <v>61336400</v>
+        <v>66447800</v>
       </c>
       <c r="G54" s="3">
-        <v>56661100</v>
+        <v>61382900</v>
       </c>
       <c r="H54" s="3">
-        <v>52827300</v>
+        <v>57229500</v>
       </c>
       <c r="I54" s="3">
-        <v>48938000</v>
+        <v>53016100</v>
       </c>
       <c r="J54" s="3">
-        <v>47102700</v>
+        <v>51027900</v>
       </c>
       <c r="K54" s="3">
         <v>40524300</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1431100</v>
+        <v>1550300</v>
       </c>
       <c r="E57" s="3">
-        <v>942400</v>
+        <v>1020900</v>
       </c>
       <c r="F57" s="3">
-        <v>740900</v>
+        <v>802700</v>
       </c>
       <c r="G57" s="3">
-        <v>821600</v>
+        <v>890100</v>
       </c>
       <c r="H57" s="3">
-        <v>726000</v>
+        <v>786500</v>
       </c>
       <c r="I57" s="3">
-        <v>742400</v>
+        <v>804300</v>
       </c>
       <c r="J57" s="3">
-        <v>693000</v>
+        <v>750700</v>
       </c>
       <c r="K57" s="3">
         <v>430900</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2693800</v>
+        <v>2918300</v>
       </c>
       <c r="E58" s="3">
-        <v>1881200</v>
+        <v>2037900</v>
       </c>
       <c r="F58" s="3">
-        <v>1783100</v>
+        <v>1931700</v>
       </c>
       <c r="G58" s="3">
-        <v>2682200</v>
+        <v>2905700</v>
       </c>
       <c r="H58" s="3">
-        <v>3633600</v>
+        <v>3936400</v>
       </c>
       <c r="I58" s="3">
-        <v>3205000</v>
+        <v>3472100</v>
       </c>
       <c r="J58" s="3">
-        <v>3332400</v>
+        <v>3610100</v>
       </c>
       <c r="K58" s="3">
         <v>2596000</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>502600</v>
+        <v>544400</v>
       </c>
       <c r="E59" s="3">
-        <v>166100</v>
+        <v>180000</v>
       </c>
       <c r="F59" s="3">
-        <v>217800</v>
+        <v>236000</v>
       </c>
       <c r="G59" s="3">
-        <v>184200</v>
+        <v>199500</v>
       </c>
       <c r="H59" s="3">
-        <v>167800</v>
+        <v>181800</v>
       </c>
       <c r="I59" s="3">
-        <v>106800</v>
+        <v>115700</v>
       </c>
       <c r="J59" s="3">
-        <v>162000</v>
+        <v>175500</v>
       </c>
       <c r="K59" s="3">
         <v>160500</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7327000</v>
+        <v>7937600</v>
       </c>
       <c r="E61" s="3">
-        <v>5810500</v>
+        <v>6294700</v>
       </c>
       <c r="F61" s="3">
-        <v>6604300</v>
+        <v>7154700</v>
       </c>
       <c r="G61" s="3">
-        <v>6344300</v>
+        <v>6873000</v>
       </c>
       <c r="H61" s="3">
-        <v>5852300</v>
+        <v>6340000</v>
       </c>
       <c r="I61" s="3">
-        <v>5744600</v>
+        <v>6223300</v>
       </c>
       <c r="J61" s="3">
-        <v>6295600</v>
+        <v>6820200</v>
       </c>
       <c r="K61" s="3">
         <v>6007800</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>435800</v>
+        <v>472200</v>
       </c>
       <c r="E62" s="3">
-        <v>514300</v>
+        <v>557100</v>
       </c>
       <c r="F62" s="3">
-        <v>534400</v>
+        <v>578900</v>
       </c>
       <c r="G62" s="3">
-        <v>595600</v>
+        <v>645200</v>
       </c>
       <c r="H62" s="3">
-        <v>504200</v>
+        <v>546300</v>
       </c>
       <c r="I62" s="3">
-        <v>533300</v>
+        <v>577700</v>
       </c>
       <c r="J62" s="3">
-        <v>500200</v>
+        <v>541800</v>
       </c>
       <c r="K62" s="3">
         <v>305100</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>75294200</v>
+        <v>81568700</v>
       </c>
       <c r="E66" s="3">
-        <v>61829000</v>
+        <v>66981400</v>
       </c>
       <c r="F66" s="3">
-        <v>54965600</v>
+        <v>59546100</v>
       </c>
       <c r="G66" s="3">
-        <v>50209000</v>
+        <v>54393100</v>
       </c>
       <c r="H66" s="3">
-        <v>46863500</v>
+        <v>50768800</v>
       </c>
       <c r="I66" s="3">
-        <v>43390900</v>
+        <v>47006800</v>
       </c>
       <c r="J66" s="3">
-        <v>41998400</v>
+        <v>45498300</v>
       </c>
       <c r="K66" s="3">
         <v>36475600</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>6240900</v>
+        <v>6761000</v>
       </c>
       <c r="E72" s="3">
-        <v>5288500</v>
+        <v>5729200</v>
       </c>
       <c r="F72" s="3">
-        <v>4327100</v>
+        <v>4687700</v>
       </c>
       <c r="G72" s="3">
-        <v>4375800</v>
+        <v>4740400</v>
       </c>
       <c r="H72" s="3">
-        <v>3913600</v>
+        <v>4239700</v>
       </c>
       <c r="I72" s="3">
-        <v>3654100</v>
+        <v>3958600</v>
       </c>
       <c r="J72" s="3">
-        <v>3326800</v>
+        <v>3604000</v>
       </c>
       <c r="K72" s="3">
         <v>2465000</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9381300</v>
+        <v>10163100</v>
       </c>
       <c r="E76" s="3">
-        <v>7736200</v>
+        <v>8380900</v>
       </c>
       <c r="F76" s="3">
-        <v>6370900</v>
+        <v>6901800</v>
       </c>
       <c r="G76" s="3">
-        <v>6452100</v>
+        <v>6989800</v>
       </c>
       <c r="H76" s="3">
-        <v>5963700</v>
+        <v>6460700</v>
       </c>
       <c r="I76" s="3">
-        <v>5547100</v>
+        <v>6009400</v>
       </c>
       <c r="J76" s="3">
-        <v>5104200</v>
+        <v>5529600</v>
       </c>
       <c r="K76" s="3">
         <v>4048700</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1628000</v>
+        <v>1763700</v>
       </c>
       <c r="E81" s="3">
-        <v>980800</v>
+        <v>1062600</v>
       </c>
       <c r="F81" s="3">
-        <v>66200</v>
+        <v>71800</v>
       </c>
       <c r="G81" s="3">
-        <v>748200</v>
+        <v>810500</v>
       </c>
       <c r="H81" s="3">
-        <v>638100</v>
+        <v>691300</v>
       </c>
       <c r="I81" s="3">
-        <v>627600</v>
+        <v>679900</v>
       </c>
       <c r="J81" s="3">
-        <v>687700</v>
+        <v>745000</v>
       </c>
       <c r="K81" s="3">
         <v>529000</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>227900</v>
+        <v>246900</v>
       </c>
       <c r="E83" s="3">
-        <v>205200</v>
+        <v>222300</v>
       </c>
       <c r="F83" s="3">
-        <v>176700</v>
+        <v>191500</v>
       </c>
       <c r="G83" s="3">
-        <v>162500</v>
+        <v>176100</v>
       </c>
       <c r="H83" s="3">
-        <v>112300</v>
+        <v>121600</v>
       </c>
       <c r="I83" s="3">
-        <v>103900</v>
+        <v>112600</v>
       </c>
       <c r="J83" s="3">
-        <v>115900</v>
+        <v>125600</v>
       </c>
       <c r="K83" s="3">
         <v>101100</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1575400</v>
+        <v>1706700</v>
       </c>
       <c r="E89" s="3">
-        <v>1462900</v>
+        <v>1584800</v>
       </c>
       <c r="F89" s="3">
-        <v>2695300</v>
+        <v>2919900</v>
       </c>
       <c r="G89" s="3">
-        <v>2955700</v>
+        <v>3202100</v>
       </c>
       <c r="H89" s="3">
-        <v>250300</v>
+        <v>271100</v>
       </c>
       <c r="I89" s="3">
-        <v>705500</v>
+        <v>764300</v>
       </c>
       <c r="J89" s="3">
-        <v>864300</v>
+        <v>936400</v>
       </c>
       <c r="K89" s="3">
         <v>389900</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-849300</v>
+        <v>-920100</v>
       </c>
       <c r="E91" s="3">
-        <v>-524600</v>
+        <v>-568300</v>
       </c>
       <c r="F91" s="3">
-        <v>-367200</v>
+        <v>-397800</v>
       </c>
       <c r="G91" s="3">
-        <v>-373300</v>
+        <v>-404400</v>
       </c>
       <c r="H91" s="3">
-        <v>-243400</v>
+        <v>-263700</v>
       </c>
       <c r="I91" s="3">
-        <v>-271700</v>
+        <v>-294300</v>
       </c>
       <c r="J91" s="3">
-        <v>-259800</v>
+        <v>-281500</v>
       </c>
       <c r="K91" s="3">
         <v>-202000</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1117100</v>
+        <v>-1210200</v>
       </c>
       <c r="E94" s="3">
-        <v>-156100</v>
+        <v>-169100</v>
       </c>
       <c r="F94" s="3">
-        <v>-1805300</v>
+        <v>-1955700</v>
       </c>
       <c r="G94" s="3">
-        <v>-525800</v>
+        <v>-569600</v>
       </c>
       <c r="H94" s="3">
-        <v>-331600</v>
+        <v>-359300</v>
       </c>
       <c r="I94" s="3">
-        <v>-457900</v>
+        <v>-496100</v>
       </c>
       <c r="J94" s="3">
-        <v>-246600</v>
+        <v>-267200</v>
       </c>
       <c r="K94" s="3">
         <v>29800</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-554600</v>
+        <v>-600800</v>
       </c>
       <c r="E96" s="3">
-        <v>-112100</v>
+        <v>-121500</v>
       </c>
       <c r="F96" s="3">
-        <v>-373400</v>
+        <v>-404500</v>
       </c>
       <c r="G96" s="3">
-        <v>-247800</v>
+        <v>-268400</v>
       </c>
       <c r="H96" s="3">
-        <v>-176600</v>
+        <v>-191300</v>
       </c>
       <c r="I96" s="3">
-        <v>-270300</v>
+        <v>-292800</v>
       </c>
       <c r="J96" s="3">
-        <v>-201700</v>
+        <v>-218500</v>
       </c>
       <c r="K96" s="3">
         <v>-164900</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>204800</v>
+        <v>221900</v>
       </c>
       <c r="E100" s="3">
-        <v>-1634400</v>
+        <v>-1770600</v>
       </c>
       <c r="F100" s="3">
-        <v>-1179700</v>
+        <v>-1278000</v>
       </c>
       <c r="G100" s="3">
-        <v>-1262600</v>
+        <v>-1367800</v>
       </c>
       <c r="H100" s="3">
-        <v>-175900</v>
+        <v>-190500</v>
       </c>
       <c r="I100" s="3">
-        <v>-869000</v>
+        <v>-941400</v>
       </c>
       <c r="J100" s="3">
-        <v>-82500</v>
+        <v>-89400</v>
       </c>
       <c r="K100" s="3">
         <v>-48600</v>
@@ -4204,25 +4204,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>852500</v>
+        <v>923600</v>
       </c>
       <c r="E101" s="3">
-        <v>718500</v>
+        <v>778400</v>
       </c>
       <c r="F101" s="3">
-        <v>280900</v>
+        <v>304300</v>
       </c>
       <c r="G101" s="3">
-        <v>34400</v>
+        <v>37200</v>
       </c>
       <c r="H101" s="3">
-        <v>392800</v>
+        <v>425600</v>
       </c>
       <c r="I101" s="3">
-        <v>70800</v>
+        <v>76600</v>
       </c>
       <c r="J101" s="3">
-        <v>-138100</v>
+        <v>-149600</v>
       </c>
       <c r="K101" s="3">
         <v>750000</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1515700</v>
+        <v>1642000</v>
       </c>
       <c r="E102" s="3">
-        <v>390900</v>
+        <v>423500</v>
       </c>
       <c r="F102" s="3">
-        <v>-8900</v>
+        <v>-9600</v>
       </c>
       <c r="G102" s="3">
-        <v>1201700</v>
+        <v>1301900</v>
       </c>
       <c r="H102" s="3">
-        <v>135600</v>
+        <v>146900</v>
       </c>
       <c r="I102" s="3">
-        <v>-550700</v>
+        <v>-596600</v>
       </c>
       <c r="J102" s="3">
-        <v>397100</v>
+        <v>430200</v>
       </c>
       <c r="K102" s="3">
         <v>1121100</v>

--- a/AAII_Financials/Yearly/CIB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CIB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>CIB</t>
   </si>
@@ -656,111 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6922600</v>
+        <v>9301000</v>
       </c>
       <c r="E8" s="3">
-        <v>4186500</v>
+        <v>6656400</v>
       </c>
       <c r="F8" s="3">
-        <v>4426900</v>
+        <v>4025500</v>
       </c>
       <c r="G8" s="3">
-        <v>4566500</v>
+        <v>4256600</v>
       </c>
       <c r="H8" s="3">
-        <v>4196200</v>
+        <v>4390900</v>
       </c>
       <c r="I8" s="3">
-        <v>4357100</v>
+        <v>4034800</v>
       </c>
       <c r="J8" s="3">
+        <v>4189500</v>
+      </c>
+      <c r="K8" s="3">
         <v>4095900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2359900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2408700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2195300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2298600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1962000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -800,9 +806,12 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -842,9 +851,12 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,9 +960,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -986,51 +1005,57 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-246900</v>
+        <v>-269600</v>
       </c>
       <c r="E15" s="3">
-        <v>-222300</v>
+        <v>-237400</v>
       </c>
       <c r="F15" s="3">
-        <v>-191500</v>
+        <v>-213800</v>
       </c>
       <c r="G15" s="3">
-        <v>-176100</v>
+        <v>-184100</v>
       </c>
       <c r="H15" s="3">
-        <v>-121200</v>
+        <v>-169300</v>
       </c>
       <c r="I15" s="3">
-        <v>-112600</v>
+        <v>-116500</v>
       </c>
       <c r="J15" s="3">
+        <v>-108300</v>
+      </c>
+      <c r="K15" s="3">
         <v>-124500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-96800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-355400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-137100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-109600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-90500</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3180900</v>
+        <v>6032500</v>
       </c>
       <c r="E17" s="3">
-        <v>1760700</v>
+        <v>3058500</v>
       </c>
       <c r="F17" s="3">
-        <v>3481300</v>
+        <v>1693000</v>
       </c>
       <c r="G17" s="3">
-        <v>2493600</v>
+        <v>3347400</v>
       </c>
       <c r="H17" s="3">
-        <v>2474200</v>
+        <v>2397700</v>
       </c>
       <c r="I17" s="3">
-        <v>2522400</v>
+        <v>2379000</v>
       </c>
       <c r="J17" s="3">
+        <v>2425400</v>
+      </c>
+      <c r="K17" s="3">
         <v>2283900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1198200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1042100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1219400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1240600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>951200</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3741800</v>
+        <v>3268500</v>
       </c>
       <c r="E18" s="3">
-        <v>2425800</v>
+        <v>3597800</v>
       </c>
       <c r="F18" s="3">
-        <v>945600</v>
+        <v>2332500</v>
       </c>
       <c r="G18" s="3">
-        <v>2072900</v>
+        <v>909200</v>
       </c>
       <c r="H18" s="3">
-        <v>1722000</v>
+        <v>1993100</v>
       </c>
       <c r="I18" s="3">
-        <v>1834700</v>
+        <v>1655700</v>
       </c>
       <c r="J18" s="3">
+        <v>1764100</v>
+      </c>
+      <c r="K18" s="3">
         <v>1812000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1161800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1366500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>975900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1058000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1010800</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,92 +1178,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1208100</v>
+        <v>-1231600</v>
       </c>
       <c r="E20" s="3">
-        <v>-870000</v>
+        <v>-1161700</v>
       </c>
       <c r="F20" s="3">
-        <v>-865300</v>
+        <v>-836500</v>
       </c>
       <c r="G20" s="3">
-        <v>-908700</v>
+        <v>-832100</v>
       </c>
       <c r="H20" s="3">
-        <v>-781800</v>
+        <v>-873800</v>
       </c>
       <c r="I20" s="3">
-        <v>-796500</v>
+        <v>-751800</v>
       </c>
       <c r="J20" s="3">
+        <v>-765900</v>
+      </c>
+      <c r="K20" s="3">
         <v>-780300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-482300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-559300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-454200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-405600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-302700</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2780500</v>
+        <v>2307600</v>
       </c>
       <c r="E21" s="3">
-        <v>1778200</v>
+        <v>2673600</v>
       </c>
       <c r="F21" s="3">
-        <v>271700</v>
+        <v>1709800</v>
       </c>
       <c r="G21" s="3">
-        <v>1340200</v>
+        <v>261300</v>
       </c>
       <c r="H21" s="3">
-        <v>1061700</v>
+        <v>1288700</v>
       </c>
       <c r="I21" s="3">
-        <v>1150700</v>
+        <v>1020900</v>
       </c>
       <c r="J21" s="3">
+        <v>1106500</v>
+      </c>
+      <c r="K21" s="3">
         <v>1157300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>780600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>924700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>730100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>814700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>838300</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1271,93 +1310,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2533600</v>
+        <v>2036900</v>
       </c>
       <c r="E23" s="3">
-        <v>1555800</v>
+        <v>2436200</v>
       </c>
       <c r="F23" s="3">
-        <v>80300</v>
+        <v>1496000</v>
       </c>
       <c r="G23" s="3">
-        <v>1164200</v>
+        <v>77200</v>
       </c>
       <c r="H23" s="3">
-        <v>940100</v>
+        <v>1119400</v>
       </c>
       <c r="I23" s="3">
-        <v>1038100</v>
+        <v>904000</v>
       </c>
       <c r="J23" s="3">
+        <v>998200</v>
+      </c>
+      <c r="K23" s="3">
         <v>1031800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>679500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>807200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>521700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>652500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>708100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>714600</v>
+        <v>483100</v>
       </c>
       <c r="E24" s="3">
-        <v>461800</v>
+        <v>687100</v>
       </c>
       <c r="F24" s="3">
-        <v>-1700</v>
+        <v>444100</v>
       </c>
       <c r="G24" s="3">
-        <v>328400</v>
+        <v>-1600</v>
       </c>
       <c r="H24" s="3">
-        <v>215700</v>
+        <v>315700</v>
       </c>
       <c r="I24" s="3">
-        <v>322000</v>
+        <v>207400</v>
       </c>
       <c r="J24" s="3">
+        <v>309600</v>
+      </c>
+      <c r="K24" s="3">
         <v>306000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>136300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>191800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>112600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>140100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>155300</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1819100</v>
+        <v>1553700</v>
       </c>
       <c r="E26" s="3">
-        <v>1094000</v>
+        <v>1749100</v>
       </c>
       <c r="F26" s="3">
-        <v>82000</v>
+        <v>1051900</v>
       </c>
       <c r="G26" s="3">
-        <v>835800</v>
+        <v>78800</v>
       </c>
       <c r="H26" s="3">
-        <v>724500</v>
+        <v>803600</v>
       </c>
       <c r="I26" s="3">
-        <v>716100</v>
+        <v>696600</v>
       </c>
       <c r="J26" s="3">
+        <v>688500</v>
+      </c>
+      <c r="K26" s="3">
         <v>725800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>543100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>615400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>409100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>512300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>552800</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1763700</v>
+        <v>1529200</v>
       </c>
       <c r="E27" s="3">
-        <v>1062600</v>
+        <v>1695900</v>
       </c>
       <c r="F27" s="3">
-        <v>71800</v>
+        <v>1021700</v>
       </c>
       <c r="G27" s="3">
-        <v>810500</v>
+        <v>69000</v>
       </c>
       <c r="H27" s="3">
-        <v>691300</v>
+        <v>779300</v>
       </c>
       <c r="I27" s="3">
-        <v>679900</v>
+        <v>664700</v>
       </c>
       <c r="J27" s="3">
+        <v>653800</v>
+      </c>
+      <c r="K27" s="3">
         <v>702500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>524200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>414900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>255600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>286600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>194100</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1547,27 +1607,30 @@
       <c r="I29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J29" s="3">
+      <c r="J29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K29" s="3">
         <v>42500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>4700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>16300</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O29" s="3">
         <v>8800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>28700</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1208100</v>
+        <v>1231600</v>
       </c>
       <c r="E32" s="3">
-        <v>870000</v>
+        <v>1161700</v>
       </c>
       <c r="F32" s="3">
-        <v>865300</v>
+        <v>836500</v>
       </c>
       <c r="G32" s="3">
-        <v>908700</v>
+        <v>832100</v>
       </c>
       <c r="H32" s="3">
-        <v>781800</v>
+        <v>873800</v>
       </c>
       <c r="I32" s="3">
-        <v>796500</v>
+        <v>751800</v>
       </c>
       <c r="J32" s="3">
+        <v>765900</v>
+      </c>
+      <c r="K32" s="3">
         <v>780300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>482300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>559300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>454200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>405600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>302700</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1763700</v>
+        <v>1529200</v>
       </c>
       <c r="E33" s="3">
-        <v>1062600</v>
+        <v>1695900</v>
       </c>
       <c r="F33" s="3">
-        <v>71800</v>
+        <v>1021700</v>
       </c>
       <c r="G33" s="3">
-        <v>810500</v>
+        <v>69000</v>
       </c>
       <c r="H33" s="3">
-        <v>691300</v>
+        <v>779300</v>
       </c>
       <c r="I33" s="3">
-        <v>679900</v>
+        <v>664700</v>
       </c>
       <c r="J33" s="3">
+        <v>653800</v>
+      </c>
+      <c r="K33" s="3">
         <v>745000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>529000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>431300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>255600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>295400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>222800</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1763700</v>
+        <v>1529200</v>
       </c>
       <c r="E35" s="3">
-        <v>1062600</v>
+        <v>1695900</v>
       </c>
       <c r="F35" s="3">
-        <v>71800</v>
+        <v>1021700</v>
       </c>
       <c r="G35" s="3">
-        <v>810500</v>
+        <v>69000</v>
       </c>
       <c r="H35" s="3">
-        <v>691300</v>
+        <v>779300</v>
       </c>
       <c r="I35" s="3">
-        <v>679900</v>
+        <v>664700</v>
       </c>
       <c r="J35" s="3">
+        <v>653800</v>
+      </c>
+      <c r="K35" s="3">
         <v>745000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>529000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>431300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>255600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>295400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>222800</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,92 +1986,99 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6427500</v>
+        <v>6993700</v>
       </c>
       <c r="E41" s="3">
-        <v>6018400</v>
+        <v>6180300</v>
       </c>
       <c r="F41" s="3">
-        <v>5248100</v>
+        <v>5786900</v>
       </c>
       <c r="G41" s="3">
-        <v>4746600</v>
+        <v>5046300</v>
       </c>
       <c r="H41" s="3">
-        <v>4116600</v>
+        <v>4564000</v>
       </c>
       <c r="I41" s="3">
-        <v>4036000</v>
+        <v>3958300</v>
       </c>
       <c r="J41" s="3">
+        <v>3880800</v>
+      </c>
+      <c r="K41" s="3">
         <v>4216400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3002000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5820800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3085400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2143200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2250000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4735000</v>
+        <v>5941600</v>
       </c>
       <c r="E42" s="3">
-        <v>2471000</v>
+        <v>4552900</v>
       </c>
       <c r="F42" s="3">
-        <v>2807400</v>
+        <v>2375900</v>
       </c>
       <c r="G42" s="3">
-        <v>3002200</v>
+        <v>2699400</v>
       </c>
       <c r="H42" s="3">
-        <v>2251100</v>
+        <v>2886700</v>
       </c>
       <c r="I42" s="3">
-        <v>1989700</v>
+        <v>2164600</v>
       </c>
       <c r="J42" s="3">
+        <v>1913100</v>
+      </c>
+      <c r="K42" s="3">
         <v>2371000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2133100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4265100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2951300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2353500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1624400</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2026,9 +2118,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2068,9 +2163,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2110,9 +2208,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2152,135 +2253,147 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>758100</v>
+        <v>749400</v>
       </c>
       <c r="E47" s="3">
-        <v>707300</v>
+        <v>728900</v>
       </c>
       <c r="F47" s="3">
-        <v>651600</v>
+        <v>680100</v>
       </c>
       <c r="G47" s="3">
-        <v>615600</v>
+        <v>626600</v>
       </c>
       <c r="H47" s="3">
-        <v>558900</v>
+        <v>591900</v>
       </c>
       <c r="I47" s="3">
-        <v>406900</v>
+        <v>537400</v>
       </c>
       <c r="J47" s="3">
+        <v>391300</v>
+      </c>
+      <c r="K47" s="3">
         <v>337500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>114800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>350900</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3262500</v>
+        <v>3216600</v>
       </c>
       <c r="E48" s="3">
-        <v>2581500</v>
+        <v>3137100</v>
       </c>
       <c r="F48" s="3">
-        <v>2288700</v>
+        <v>2482200</v>
       </c>
       <c r="G48" s="3">
-        <v>1953400</v>
+        <v>2200700</v>
       </c>
       <c r="H48" s="3">
-        <v>1326400</v>
+        <v>1878200</v>
       </c>
       <c r="I48" s="3">
-        <v>1244100</v>
+        <v>1275400</v>
       </c>
       <c r="J48" s="3">
+        <v>1196200</v>
+      </c>
+      <c r="K48" s="3">
         <v>1221300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>996800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1611800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>591800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>905700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>886300</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2714200</v>
+        <v>2122400</v>
       </c>
       <c r="E49" s="3">
-        <v>2243500</v>
+        <v>2609800</v>
       </c>
       <c r="F49" s="3">
-        <v>1951900</v>
+        <v>2157200</v>
       </c>
       <c r="G49" s="3">
-        <v>1880700</v>
+        <v>1876800</v>
       </c>
       <c r="H49" s="3">
-        <v>1872500</v>
+        <v>1808300</v>
       </c>
       <c r="I49" s="3">
-        <v>1724200</v>
+        <v>1800500</v>
       </c>
       <c r="J49" s="3">
+        <v>1657900</v>
+      </c>
+      <c r="K49" s="3">
         <v>1740400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1489400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2224700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>969100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>171400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>224400</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>198800</v>
+        <v>171400</v>
       </c>
       <c r="E52" s="3">
-        <v>194100</v>
+        <v>191100</v>
       </c>
       <c r="F52" s="3">
-        <v>175600</v>
+        <v>186600</v>
       </c>
       <c r="G52" s="3">
-        <v>104300</v>
+        <v>168800</v>
       </c>
       <c r="H52" s="3">
-        <v>70500</v>
+        <v>100300</v>
       </c>
       <c r="I52" s="3">
-        <v>38600</v>
+        <v>67800</v>
       </c>
       <c r="J52" s="3">
+        <v>37200</v>
+      </c>
+      <c r="K52" s="3">
         <v>57900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>48800</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>91731800</v>
+        <v>85732200</v>
       </c>
       <c r="E54" s="3">
-        <v>75362300</v>
+        <v>88203700</v>
       </c>
       <c r="F54" s="3">
-        <v>66447800</v>
+        <v>72463800</v>
       </c>
       <c r="G54" s="3">
-        <v>61382900</v>
+        <v>63892100</v>
       </c>
       <c r="H54" s="3">
-        <v>57229500</v>
+        <v>59022000</v>
       </c>
       <c r="I54" s="3">
-        <v>53016100</v>
+        <v>55028400</v>
       </c>
       <c r="J54" s="3">
+        <v>50977100</v>
+      </c>
+      <c r="K54" s="3">
         <v>51027900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>40524300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>38903800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35320400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29374900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>28202800</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,134 +2654,144 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1550300</v>
+        <v>1599900</v>
       </c>
       <c r="E57" s="3">
-        <v>1020900</v>
+        <v>1490700</v>
       </c>
       <c r="F57" s="3">
-        <v>802700</v>
+        <v>981700</v>
       </c>
       <c r="G57" s="3">
-        <v>890100</v>
+        <v>771800</v>
       </c>
       <c r="H57" s="3">
-        <v>786500</v>
+        <v>855800</v>
       </c>
       <c r="I57" s="3">
-        <v>804300</v>
+        <v>756200</v>
       </c>
       <c r="J57" s="3">
+        <v>773300</v>
+      </c>
+      <c r="K57" s="3">
         <v>750700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>430900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1233800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>705000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>850500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>848300</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2918300</v>
+        <v>1987300</v>
       </c>
       <c r="E58" s="3">
-        <v>2037900</v>
+        <v>2806000</v>
       </c>
       <c r="F58" s="3">
-        <v>1931700</v>
+        <v>1959600</v>
       </c>
       <c r="G58" s="3">
-        <v>2905700</v>
+        <v>1857400</v>
       </c>
       <c r="H58" s="3">
-        <v>3936400</v>
+        <v>2794000</v>
       </c>
       <c r="I58" s="3">
-        <v>3472100</v>
+        <v>3785000</v>
       </c>
       <c r="J58" s="3">
+        <v>3338600</v>
+      </c>
+      <c r="K58" s="3">
         <v>3610100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2596000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3286400</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>544400</v>
+        <v>358000</v>
       </c>
       <c r="E59" s="3">
-        <v>180000</v>
+        <v>523500</v>
       </c>
       <c r="F59" s="3">
-        <v>236000</v>
+        <v>173000</v>
       </c>
       <c r="G59" s="3">
-        <v>199500</v>
+        <v>226900</v>
       </c>
       <c r="H59" s="3">
-        <v>181800</v>
+        <v>191900</v>
       </c>
       <c r="I59" s="3">
-        <v>115700</v>
+        <v>174800</v>
       </c>
       <c r="J59" s="3">
+        <v>111300</v>
+      </c>
+      <c r="K59" s="3">
         <v>175500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>160500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>420200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>279100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>103500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>92500</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2692,93 +2831,102 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7937600</v>
+        <v>6180200</v>
       </c>
       <c r="E61" s="3">
-        <v>6294700</v>
+        <v>7632300</v>
       </c>
       <c r="F61" s="3">
-        <v>7154700</v>
+        <v>6052600</v>
       </c>
       <c r="G61" s="3">
-        <v>6873000</v>
+        <v>6879500</v>
       </c>
       <c r="H61" s="3">
-        <v>6340000</v>
+        <v>6608600</v>
       </c>
       <c r="I61" s="3">
-        <v>6223300</v>
+        <v>6096200</v>
       </c>
       <c r="J61" s="3">
+        <v>5983900</v>
+      </c>
+      <c r="K61" s="3">
         <v>6820200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6007800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5284900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6705800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3617800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3402000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>472200</v>
+        <v>767300</v>
       </c>
       <c r="E62" s="3">
-        <v>557100</v>
+        <v>454000</v>
       </c>
       <c r="F62" s="3">
-        <v>578900</v>
+        <v>535700</v>
       </c>
       <c r="G62" s="3">
-        <v>645200</v>
+        <v>556700</v>
       </c>
       <c r="H62" s="3">
-        <v>546300</v>
+        <v>620400</v>
       </c>
       <c r="I62" s="3">
-        <v>577700</v>
+        <v>525300</v>
       </c>
       <c r="J62" s="3">
+        <v>555500</v>
+      </c>
+      <c r="K62" s="3">
         <v>541800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>305100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>275100</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P62" s="3">
         <v>40100</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>81568700</v>
+        <v>76209800</v>
       </c>
       <c r="E66" s="3">
-        <v>66981400</v>
+        <v>78431500</v>
       </c>
       <c r="F66" s="3">
-        <v>59546100</v>
+        <v>64405200</v>
       </c>
       <c r="G66" s="3">
-        <v>54393100</v>
+        <v>57255800</v>
       </c>
       <c r="H66" s="3">
-        <v>50768800</v>
+        <v>52301000</v>
       </c>
       <c r="I66" s="3">
-        <v>47006800</v>
+        <v>48816200</v>
       </c>
       <c r="J66" s="3">
+        <v>45198800</v>
+      </c>
+      <c r="K66" s="3">
         <v>45498300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36475600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>34517100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>31947300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25892800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>25235000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3083,14 +3250,17 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>55000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>50000</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>6761000</v>
+        <v>7172100</v>
       </c>
       <c r="E72" s="3">
-        <v>5729200</v>
+        <v>6501000</v>
       </c>
       <c r="F72" s="3">
-        <v>4687700</v>
+        <v>5508900</v>
       </c>
       <c r="G72" s="3">
-        <v>4740400</v>
+        <v>4507400</v>
       </c>
       <c r="H72" s="3">
-        <v>4239700</v>
+        <v>4558100</v>
       </c>
       <c r="I72" s="3">
-        <v>3958600</v>
+        <v>4076600</v>
       </c>
       <c r="J72" s="3">
+        <v>3806300</v>
+      </c>
+      <c r="K72" s="3">
         <v>3604000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2465000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6803400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3027200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2283500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2217600</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>10163100</v>
+        <v>9522400</v>
       </c>
       <c r="E76" s="3">
-        <v>8380900</v>
+        <v>9772200</v>
       </c>
       <c r="F76" s="3">
-        <v>6901800</v>
+        <v>8058600</v>
       </c>
       <c r="G76" s="3">
-        <v>6989800</v>
+        <v>6636300</v>
       </c>
       <c r="H76" s="3">
-        <v>6460700</v>
+        <v>6721000</v>
       </c>
       <c r="I76" s="3">
-        <v>6009400</v>
+        <v>6212200</v>
       </c>
       <c r="J76" s="3">
+        <v>5778200</v>
+      </c>
+      <c r="K76" s="3">
         <v>5529600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4048700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4386700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3373100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3427100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2917800</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1763700</v>
+        <v>1529200</v>
       </c>
       <c r="E81" s="3">
-        <v>1062600</v>
+        <v>1695900</v>
       </c>
       <c r="F81" s="3">
-        <v>71800</v>
+        <v>1021700</v>
       </c>
       <c r="G81" s="3">
-        <v>810500</v>
+        <v>69000</v>
       </c>
       <c r="H81" s="3">
-        <v>691300</v>
+        <v>779300</v>
       </c>
       <c r="I81" s="3">
-        <v>679900</v>
+        <v>664700</v>
       </c>
       <c r="J81" s="3">
+        <v>653800</v>
+      </c>
+      <c r="K81" s="3">
         <v>745000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>529000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>431300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>255600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>295400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>222800</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>246900</v>
+        <v>270700</v>
       </c>
       <c r="E83" s="3">
-        <v>222300</v>
+        <v>237400</v>
       </c>
       <c r="F83" s="3">
-        <v>191500</v>
+        <v>213800</v>
       </c>
       <c r="G83" s="3">
-        <v>176100</v>
+        <v>184100</v>
       </c>
       <c r="H83" s="3">
-        <v>121600</v>
+        <v>169300</v>
       </c>
       <c r="I83" s="3">
-        <v>112600</v>
+        <v>116900</v>
       </c>
       <c r="J83" s="3">
+        <v>108300</v>
+      </c>
+      <c r="K83" s="3">
         <v>125600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>101100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>113200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>208400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>162200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>130200</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1706700</v>
+        <v>4788300</v>
       </c>
       <c r="E89" s="3">
-        <v>1584800</v>
+        <v>1641100</v>
       </c>
       <c r="F89" s="3">
-        <v>2919900</v>
+        <v>1523800</v>
       </c>
       <c r="G89" s="3">
-        <v>3202100</v>
+        <v>2807600</v>
       </c>
       <c r="H89" s="3">
-        <v>271100</v>
+        <v>3078900</v>
       </c>
       <c r="I89" s="3">
-        <v>764300</v>
+        <v>260700</v>
       </c>
       <c r="J89" s="3">
+        <v>734900</v>
+      </c>
+      <c r="K89" s="3">
         <v>936400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>389900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1733500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1421800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>541900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1299900</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-920100</v>
+        <v>-603000</v>
       </c>
       <c r="E91" s="3">
-        <v>-568300</v>
+        <v>-884700</v>
       </c>
       <c r="F91" s="3">
-        <v>-397800</v>
+        <v>-546500</v>
       </c>
       <c r="G91" s="3">
-        <v>-404400</v>
+        <v>-382500</v>
       </c>
       <c r="H91" s="3">
-        <v>-263700</v>
+        <v>-388900</v>
       </c>
       <c r="I91" s="3">
-        <v>-294300</v>
+        <v>-253500</v>
       </c>
       <c r="J91" s="3">
+        <v>-283000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-281500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-202000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-691300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-497200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-339700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-463200</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1210200</v>
+        <v>-39900</v>
       </c>
       <c r="E94" s="3">
-        <v>-169100</v>
+        <v>-1163600</v>
       </c>
       <c r="F94" s="3">
-        <v>-1955700</v>
+        <v>-162600</v>
       </c>
       <c r="G94" s="3">
-        <v>-569600</v>
+        <v>-1880500</v>
       </c>
       <c r="H94" s="3">
-        <v>-359300</v>
+        <v>-547700</v>
       </c>
       <c r="I94" s="3">
-        <v>-496100</v>
+        <v>-345500</v>
       </c>
       <c r="J94" s="3">
+        <v>-477000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-267200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>29800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>242900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-898400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-178300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-171500</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-600800</v>
+        <v>-824500</v>
       </c>
       <c r="E96" s="3">
-        <v>-121500</v>
+        <v>-577700</v>
       </c>
       <c r="F96" s="3">
-        <v>-404500</v>
+        <v>-116800</v>
       </c>
       <c r="G96" s="3">
-        <v>-268400</v>
+        <v>-389000</v>
       </c>
       <c r="H96" s="3">
-        <v>-191300</v>
+        <v>-258100</v>
       </c>
       <c r="I96" s="3">
-        <v>-292800</v>
+        <v>-183900</v>
       </c>
       <c r="J96" s="3">
+        <v>-281600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-218500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-164900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-185600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-170600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-175000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-173800</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>221900</v>
+        <v>-1357700</v>
       </c>
       <c r="E100" s="3">
-        <v>-1770600</v>
+        <v>213400</v>
       </c>
       <c r="F100" s="3">
-        <v>-1278000</v>
+        <v>-1702500</v>
       </c>
       <c r="G100" s="3">
-        <v>-1367800</v>
+        <v>-1228900</v>
       </c>
       <c r="H100" s="3">
-        <v>-190500</v>
+        <v>-1315200</v>
       </c>
       <c r="I100" s="3">
-        <v>-941400</v>
+        <v>-183200</v>
       </c>
       <c r="J100" s="3">
+        <v>-905200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-89400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-48600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>423800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1337800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-150800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1946500</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>923600</v>
+        <v>-1352100</v>
       </c>
       <c r="E101" s="3">
-        <v>778400</v>
+        <v>888100</v>
       </c>
       <c r="F101" s="3">
-        <v>304300</v>
+        <v>748500</v>
       </c>
       <c r="G101" s="3">
-        <v>37200</v>
+        <v>292600</v>
       </c>
       <c r="H101" s="3">
-        <v>425600</v>
+        <v>35800</v>
       </c>
       <c r="I101" s="3">
-        <v>76600</v>
+        <v>409200</v>
       </c>
       <c r="J101" s="3">
+        <v>73700</v>
+      </c>
+      <c r="K101" s="3">
         <v>-149600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>750000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>552200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>93400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-80800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>44300</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1642000</v>
+        <v>2038600</v>
       </c>
       <c r="E102" s="3">
-        <v>423500</v>
+        <v>1578900</v>
       </c>
       <c r="F102" s="3">
-        <v>-9600</v>
+        <v>407200</v>
       </c>
       <c r="G102" s="3">
-        <v>1301900</v>
+        <v>-9200</v>
       </c>
       <c r="H102" s="3">
-        <v>146900</v>
+        <v>1251800</v>
       </c>
       <c r="I102" s="3">
-        <v>-596600</v>
+        <v>141300</v>
       </c>
       <c r="J102" s="3">
+        <v>-573700</v>
+      </c>
+      <c r="K102" s="3">
         <v>430200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1121100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-514600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1954700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>132000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>519400</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CIB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CIB_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>9301000</v>
+        <v>8929000</v>
       </c>
       <c r="E8" s="3">
-        <v>6656400</v>
+        <v>6390100</v>
       </c>
       <c r="F8" s="3">
-        <v>4025500</v>
+        <v>3864500</v>
       </c>
       <c r="G8" s="3">
-        <v>4256600</v>
+        <v>4086300</v>
       </c>
       <c r="H8" s="3">
-        <v>4390900</v>
+        <v>4215200</v>
       </c>
       <c r="I8" s="3">
-        <v>4034800</v>
+        <v>3873400</v>
       </c>
       <c r="J8" s="3">
-        <v>4189500</v>
+        <v>4021900</v>
       </c>
       <c r="K8" s="3">
         <v>4095900</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-269600</v>
+        <v>-258800</v>
       </c>
       <c r="E15" s="3">
-        <v>-237400</v>
+        <v>-227900</v>
       </c>
       <c r="F15" s="3">
-        <v>-213800</v>
+        <v>-205200</v>
       </c>
       <c r="G15" s="3">
-        <v>-184100</v>
+        <v>-176700</v>
       </c>
       <c r="H15" s="3">
-        <v>-169300</v>
+        <v>-162500</v>
       </c>
       <c r="I15" s="3">
-        <v>-116500</v>
+        <v>-111900</v>
       </c>
       <c r="J15" s="3">
-        <v>-108300</v>
+        <v>-103900</v>
       </c>
       <c r="K15" s="3">
         <v>-124500</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6032500</v>
+        <v>5791200</v>
       </c>
       <c r="E17" s="3">
-        <v>3058500</v>
+        <v>2936200</v>
       </c>
       <c r="F17" s="3">
-        <v>1693000</v>
+        <v>1625300</v>
       </c>
       <c r="G17" s="3">
-        <v>3347400</v>
+        <v>3213500</v>
       </c>
       <c r="H17" s="3">
-        <v>2397700</v>
+        <v>2301800</v>
       </c>
       <c r="I17" s="3">
-        <v>2379000</v>
+        <v>2283900</v>
       </c>
       <c r="J17" s="3">
-        <v>2425400</v>
+        <v>2328400</v>
       </c>
       <c r="K17" s="3">
         <v>2283900</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3268500</v>
+        <v>3137800</v>
       </c>
       <c r="E18" s="3">
-        <v>3597800</v>
+        <v>3453900</v>
       </c>
       <c r="F18" s="3">
-        <v>2332500</v>
+        <v>2239200</v>
       </c>
       <c r="G18" s="3">
-        <v>909200</v>
+        <v>872900</v>
       </c>
       <c r="H18" s="3">
-        <v>1993100</v>
+        <v>1913400</v>
       </c>
       <c r="I18" s="3">
-        <v>1655700</v>
+        <v>1589500</v>
       </c>
       <c r="J18" s="3">
-        <v>1764100</v>
+        <v>1693500</v>
       </c>
       <c r="K18" s="3">
         <v>1812000</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1231600</v>
+        <v>-1182400</v>
       </c>
       <c r="E20" s="3">
-        <v>-1161700</v>
+        <v>-1115200</v>
       </c>
       <c r="F20" s="3">
-        <v>-836500</v>
+        <v>-803000</v>
       </c>
       <c r="G20" s="3">
-        <v>-832100</v>
+        <v>-798800</v>
       </c>
       <c r="H20" s="3">
-        <v>-873800</v>
+        <v>-838800</v>
       </c>
       <c r="I20" s="3">
-        <v>-751800</v>
+        <v>-721700</v>
       </c>
       <c r="J20" s="3">
-        <v>-765900</v>
+        <v>-735300</v>
       </c>
       <c r="K20" s="3">
         <v>-780300</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2307600</v>
+        <v>2215300</v>
       </c>
       <c r="E21" s="3">
-        <v>2673600</v>
+        <v>2566600</v>
       </c>
       <c r="F21" s="3">
-        <v>1709800</v>
+        <v>1641400</v>
       </c>
       <c r="G21" s="3">
-        <v>261300</v>
+        <v>250800</v>
       </c>
       <c r="H21" s="3">
-        <v>1288700</v>
+        <v>1237100</v>
       </c>
       <c r="I21" s="3">
-        <v>1020900</v>
+        <v>980100</v>
       </c>
       <c r="J21" s="3">
-        <v>1106500</v>
+        <v>1062200</v>
       </c>
       <c r="K21" s="3">
         <v>1157300</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2036900</v>
+        <v>1955400</v>
       </c>
       <c r="E23" s="3">
-        <v>2436200</v>
+        <v>2338700</v>
       </c>
       <c r="F23" s="3">
-        <v>1496000</v>
+        <v>1436200</v>
       </c>
       <c r="G23" s="3">
-        <v>77200</v>
+        <v>74100</v>
       </c>
       <c r="H23" s="3">
-        <v>1119400</v>
+        <v>1074600</v>
       </c>
       <c r="I23" s="3">
-        <v>904000</v>
+        <v>867800</v>
       </c>
       <c r="J23" s="3">
-        <v>998200</v>
+        <v>958300</v>
       </c>
       <c r="K23" s="3">
         <v>1031800</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>483100</v>
+        <v>463800</v>
       </c>
       <c r="E24" s="3">
-        <v>687100</v>
+        <v>659600</v>
       </c>
       <c r="F24" s="3">
-        <v>444100</v>
+        <v>426300</v>
       </c>
       <c r="G24" s="3">
         <v>-1600</v>
       </c>
       <c r="H24" s="3">
-        <v>315700</v>
+        <v>303100</v>
       </c>
       <c r="I24" s="3">
-        <v>207400</v>
+        <v>199100</v>
       </c>
       <c r="J24" s="3">
-        <v>309600</v>
+        <v>297300</v>
       </c>
       <c r="K24" s="3">
         <v>306000</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1553700</v>
+        <v>1491600</v>
       </c>
       <c r="E26" s="3">
-        <v>1749100</v>
+        <v>1679100</v>
       </c>
       <c r="F26" s="3">
-        <v>1051900</v>
+        <v>1009900</v>
       </c>
       <c r="G26" s="3">
-        <v>78800</v>
+        <v>75700</v>
       </c>
       <c r="H26" s="3">
-        <v>803600</v>
+        <v>771500</v>
       </c>
       <c r="I26" s="3">
-        <v>696600</v>
+        <v>668700</v>
       </c>
       <c r="J26" s="3">
-        <v>688500</v>
+        <v>661000</v>
       </c>
       <c r="K26" s="3">
         <v>725800</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1529200</v>
+        <v>1468100</v>
       </c>
       <c r="E27" s="3">
-        <v>1695900</v>
+        <v>1628000</v>
       </c>
       <c r="F27" s="3">
-        <v>1021700</v>
+        <v>980800</v>
       </c>
       <c r="G27" s="3">
-        <v>69000</v>
+        <v>66200</v>
       </c>
       <c r="H27" s="3">
-        <v>779300</v>
+        <v>748200</v>
       </c>
       <c r="I27" s="3">
-        <v>664700</v>
+        <v>638100</v>
       </c>
       <c r="J27" s="3">
-        <v>653800</v>
+        <v>627600</v>
       </c>
       <c r="K27" s="3">
         <v>702500</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1231600</v>
+        <v>1182400</v>
       </c>
       <c r="E32" s="3">
-        <v>1161700</v>
+        <v>1115200</v>
       </c>
       <c r="F32" s="3">
-        <v>836500</v>
+        <v>803000</v>
       </c>
       <c r="G32" s="3">
-        <v>832100</v>
+        <v>798800</v>
       </c>
       <c r="H32" s="3">
-        <v>873800</v>
+        <v>838800</v>
       </c>
       <c r="I32" s="3">
-        <v>751800</v>
+        <v>721700</v>
       </c>
       <c r="J32" s="3">
-        <v>765900</v>
+        <v>735300</v>
       </c>
       <c r="K32" s="3">
         <v>780300</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1529200</v>
+        <v>1468100</v>
       </c>
       <c r="E33" s="3">
-        <v>1695900</v>
+        <v>1628000</v>
       </c>
       <c r="F33" s="3">
-        <v>1021700</v>
+        <v>980800</v>
       </c>
       <c r="G33" s="3">
-        <v>69000</v>
+        <v>66200</v>
       </c>
       <c r="H33" s="3">
-        <v>779300</v>
+        <v>748200</v>
       </c>
       <c r="I33" s="3">
-        <v>664700</v>
+        <v>638100</v>
       </c>
       <c r="J33" s="3">
-        <v>653800</v>
+        <v>627600</v>
       </c>
       <c r="K33" s="3">
         <v>745000</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1529200</v>
+        <v>1468100</v>
       </c>
       <c r="E35" s="3">
-        <v>1695900</v>
+        <v>1628000</v>
       </c>
       <c r="F35" s="3">
-        <v>1021700</v>
+        <v>980800</v>
       </c>
       <c r="G35" s="3">
-        <v>69000</v>
+        <v>66200</v>
       </c>
       <c r="H35" s="3">
-        <v>779300</v>
+        <v>748200</v>
       </c>
       <c r="I35" s="3">
-        <v>664700</v>
+        <v>638100</v>
       </c>
       <c r="J35" s="3">
-        <v>653800</v>
+        <v>627600</v>
       </c>
       <c r="K35" s="3">
         <v>745000</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6993700</v>
+        <v>6714000</v>
       </c>
       <c r="E41" s="3">
-        <v>6180300</v>
+        <v>5933100</v>
       </c>
       <c r="F41" s="3">
-        <v>5786900</v>
+        <v>5555400</v>
       </c>
       <c r="G41" s="3">
-        <v>5046300</v>
+        <v>4844400</v>
       </c>
       <c r="H41" s="3">
-        <v>4564000</v>
+        <v>4381500</v>
       </c>
       <c r="I41" s="3">
-        <v>3958300</v>
+        <v>3799900</v>
       </c>
       <c r="J41" s="3">
-        <v>3880800</v>
+        <v>3725500</v>
       </c>
       <c r="K41" s="3">
         <v>4216400</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>5941600</v>
+        <v>5703900</v>
       </c>
       <c r="E42" s="3">
-        <v>4552900</v>
+        <v>4370800</v>
       </c>
       <c r="F42" s="3">
-        <v>2375900</v>
+        <v>2280900</v>
       </c>
       <c r="G42" s="3">
-        <v>2699400</v>
+        <v>2591400</v>
       </c>
       <c r="H42" s="3">
-        <v>2886700</v>
+        <v>2771300</v>
       </c>
       <c r="I42" s="3">
-        <v>2164600</v>
+        <v>2078000</v>
       </c>
       <c r="J42" s="3">
-        <v>1913100</v>
+        <v>1836600</v>
       </c>
       <c r="K42" s="3">
         <v>2371000</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>749400</v>
+        <v>719400</v>
       </c>
       <c r="E47" s="3">
-        <v>728900</v>
+        <v>699800</v>
       </c>
       <c r="F47" s="3">
-        <v>680100</v>
+        <v>652900</v>
       </c>
       <c r="G47" s="3">
-        <v>626600</v>
+        <v>601500</v>
       </c>
       <c r="H47" s="3">
-        <v>591900</v>
+        <v>568300</v>
       </c>
       <c r="I47" s="3">
-        <v>537400</v>
+        <v>515900</v>
       </c>
       <c r="J47" s="3">
-        <v>391300</v>
+        <v>375600</v>
       </c>
       <c r="K47" s="3">
         <v>337500</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3216600</v>
+        <v>3088000</v>
       </c>
       <c r="E48" s="3">
-        <v>3137100</v>
+        <v>3011600</v>
       </c>
       <c r="F48" s="3">
-        <v>2482200</v>
+        <v>2382900</v>
       </c>
       <c r="G48" s="3">
-        <v>2200700</v>
+        <v>2112600</v>
       </c>
       <c r="H48" s="3">
-        <v>1878200</v>
+        <v>1803100</v>
       </c>
       <c r="I48" s="3">
-        <v>1275400</v>
+        <v>1224400</v>
       </c>
       <c r="J48" s="3">
-        <v>1196200</v>
+        <v>1148400</v>
       </c>
       <c r="K48" s="3">
         <v>1221300</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2122400</v>
+        <v>2037500</v>
       </c>
       <c r="E49" s="3">
-        <v>2609800</v>
+        <v>2505400</v>
       </c>
       <c r="F49" s="3">
-        <v>2157200</v>
+        <v>2070900</v>
       </c>
       <c r="G49" s="3">
-        <v>1876800</v>
+        <v>1801800</v>
       </c>
       <c r="H49" s="3">
-        <v>1808300</v>
+        <v>1736000</v>
       </c>
       <c r="I49" s="3">
-        <v>1800500</v>
+        <v>1728400</v>
       </c>
       <c r="J49" s="3">
-        <v>1657900</v>
+        <v>1591500</v>
       </c>
       <c r="K49" s="3">
         <v>1740400</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>171400</v>
+        <v>164500</v>
       </c>
       <c r="E52" s="3">
-        <v>191100</v>
+        <v>183500</v>
       </c>
       <c r="F52" s="3">
-        <v>186600</v>
+        <v>179100</v>
       </c>
       <c r="G52" s="3">
-        <v>168800</v>
+        <v>162100</v>
       </c>
       <c r="H52" s="3">
-        <v>100300</v>
+        <v>96200</v>
       </c>
       <c r="I52" s="3">
-        <v>67800</v>
+        <v>65100</v>
       </c>
       <c r="J52" s="3">
-        <v>37200</v>
+        <v>35700</v>
       </c>
       <c r="K52" s="3">
         <v>57900</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>85732200</v>
+        <v>82302900</v>
       </c>
       <c r="E54" s="3">
-        <v>88203700</v>
+        <v>84675500</v>
       </c>
       <c r="F54" s="3">
-        <v>72463800</v>
+        <v>69565200</v>
       </c>
       <c r="G54" s="3">
-        <v>63892100</v>
+        <v>61336400</v>
       </c>
       <c r="H54" s="3">
-        <v>59022000</v>
+        <v>56661100</v>
       </c>
       <c r="I54" s="3">
-        <v>55028400</v>
+        <v>52827300</v>
       </c>
       <c r="J54" s="3">
-        <v>50977100</v>
+        <v>48938000</v>
       </c>
       <c r="K54" s="3">
         <v>51027900</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1599900</v>
+        <v>1535900</v>
       </c>
       <c r="E57" s="3">
-        <v>1490700</v>
+        <v>1431100</v>
       </c>
       <c r="F57" s="3">
-        <v>981700</v>
+        <v>942400</v>
       </c>
       <c r="G57" s="3">
-        <v>771800</v>
+        <v>740900</v>
       </c>
       <c r="H57" s="3">
-        <v>855800</v>
+        <v>821600</v>
       </c>
       <c r="I57" s="3">
-        <v>756200</v>
+        <v>726000</v>
       </c>
       <c r="J57" s="3">
-        <v>773300</v>
+        <v>742400</v>
       </c>
       <c r="K57" s="3">
         <v>750700</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1987300</v>
+        <v>1907800</v>
       </c>
       <c r="E58" s="3">
-        <v>2806000</v>
+        <v>2693800</v>
       </c>
       <c r="F58" s="3">
-        <v>1959600</v>
+        <v>1881200</v>
       </c>
       <c r="G58" s="3">
-        <v>1857400</v>
+        <v>1783100</v>
       </c>
       <c r="H58" s="3">
-        <v>2794000</v>
+        <v>2682200</v>
       </c>
       <c r="I58" s="3">
-        <v>3785000</v>
+        <v>3633600</v>
       </c>
       <c r="J58" s="3">
-        <v>3338600</v>
+        <v>3205000</v>
       </c>
       <c r="K58" s="3">
         <v>3610100</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>358000</v>
+        <v>343700</v>
       </c>
       <c r="E59" s="3">
-        <v>523500</v>
+        <v>502600</v>
       </c>
       <c r="F59" s="3">
-        <v>173000</v>
+        <v>166100</v>
       </c>
       <c r="G59" s="3">
-        <v>226900</v>
+        <v>217800</v>
       </c>
       <c r="H59" s="3">
-        <v>191900</v>
+        <v>184200</v>
       </c>
       <c r="I59" s="3">
-        <v>174800</v>
+        <v>167800</v>
       </c>
       <c r="J59" s="3">
-        <v>111300</v>
+        <v>106800</v>
       </c>
       <c r="K59" s="3">
         <v>175500</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6180200</v>
+        <v>5933000</v>
       </c>
       <c r="E61" s="3">
-        <v>7632300</v>
+        <v>7327000</v>
       </c>
       <c r="F61" s="3">
-        <v>6052600</v>
+        <v>5810500</v>
       </c>
       <c r="G61" s="3">
-        <v>6879500</v>
+        <v>6604300</v>
       </c>
       <c r="H61" s="3">
-        <v>6608600</v>
+        <v>6344300</v>
       </c>
       <c r="I61" s="3">
-        <v>6096200</v>
+        <v>5852300</v>
       </c>
       <c r="J61" s="3">
-        <v>5983900</v>
+        <v>5744600</v>
       </c>
       <c r="K61" s="3">
         <v>6820200</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>767300</v>
+        <v>736600</v>
       </c>
       <c r="E62" s="3">
-        <v>454000</v>
+        <v>435800</v>
       </c>
       <c r="F62" s="3">
-        <v>535700</v>
+        <v>514300</v>
       </c>
       <c r="G62" s="3">
-        <v>556700</v>
+        <v>534400</v>
       </c>
       <c r="H62" s="3">
-        <v>620400</v>
+        <v>595600</v>
       </c>
       <c r="I62" s="3">
-        <v>525300</v>
+        <v>504200</v>
       </c>
       <c r="J62" s="3">
-        <v>555500</v>
+        <v>533300</v>
       </c>
       <c r="K62" s="3">
         <v>541800</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>76209800</v>
+        <v>73161400</v>
       </c>
       <c r="E66" s="3">
-        <v>78431500</v>
+        <v>75294200</v>
       </c>
       <c r="F66" s="3">
-        <v>64405200</v>
+        <v>61829000</v>
       </c>
       <c r="G66" s="3">
-        <v>57255800</v>
+        <v>54965600</v>
       </c>
       <c r="H66" s="3">
-        <v>52301000</v>
+        <v>50209000</v>
       </c>
       <c r="I66" s="3">
-        <v>48816200</v>
+        <v>46863500</v>
       </c>
       <c r="J66" s="3">
-        <v>45198800</v>
+        <v>43390900</v>
       </c>
       <c r="K66" s="3">
         <v>45498300</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7172100</v>
+        <v>6885200</v>
       </c>
       <c r="E72" s="3">
-        <v>6501000</v>
+        <v>6240900</v>
       </c>
       <c r="F72" s="3">
-        <v>5508900</v>
+        <v>5288500</v>
       </c>
       <c r="G72" s="3">
-        <v>4507400</v>
+        <v>4327100</v>
       </c>
       <c r="H72" s="3">
-        <v>4558100</v>
+        <v>4375800</v>
       </c>
       <c r="I72" s="3">
-        <v>4076600</v>
+        <v>3913600</v>
       </c>
       <c r="J72" s="3">
-        <v>3806300</v>
+        <v>3654100</v>
       </c>
       <c r="K72" s="3">
         <v>3604000</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9522400</v>
+        <v>9141500</v>
       </c>
       <c r="E76" s="3">
-        <v>9772200</v>
+        <v>9381300</v>
       </c>
       <c r="F76" s="3">
-        <v>8058600</v>
+        <v>7736200</v>
       </c>
       <c r="G76" s="3">
-        <v>6636300</v>
+        <v>6370900</v>
       </c>
       <c r="H76" s="3">
-        <v>6721000</v>
+        <v>6452100</v>
       </c>
       <c r="I76" s="3">
-        <v>6212200</v>
+        <v>5963700</v>
       </c>
       <c r="J76" s="3">
-        <v>5778200</v>
+        <v>5547100</v>
       </c>
       <c r="K76" s="3">
         <v>5529600</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1529200</v>
+        <v>1468100</v>
       </c>
       <c r="E81" s="3">
-        <v>1695900</v>
+        <v>1628000</v>
       </c>
       <c r="F81" s="3">
-        <v>1021700</v>
+        <v>980800</v>
       </c>
       <c r="G81" s="3">
-        <v>69000</v>
+        <v>66200</v>
       </c>
       <c r="H81" s="3">
-        <v>779300</v>
+        <v>748200</v>
       </c>
       <c r="I81" s="3">
-        <v>664700</v>
+        <v>638100</v>
       </c>
       <c r="J81" s="3">
-        <v>653800</v>
+        <v>627600</v>
       </c>
       <c r="K81" s="3">
         <v>745000</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>270700</v>
+        <v>259900</v>
       </c>
       <c r="E83" s="3">
-        <v>237400</v>
+        <v>227900</v>
       </c>
       <c r="F83" s="3">
-        <v>213800</v>
+        <v>205200</v>
       </c>
       <c r="G83" s="3">
-        <v>184100</v>
+        <v>176700</v>
       </c>
       <c r="H83" s="3">
-        <v>169300</v>
+        <v>162500</v>
       </c>
       <c r="I83" s="3">
-        <v>116900</v>
+        <v>112300</v>
       </c>
       <c r="J83" s="3">
-        <v>108300</v>
+        <v>103900</v>
       </c>
       <c r="K83" s="3">
         <v>125600</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4788300</v>
+        <v>4596700</v>
       </c>
       <c r="E89" s="3">
-        <v>1641100</v>
+        <v>1575400</v>
       </c>
       <c r="F89" s="3">
-        <v>1523800</v>
+        <v>1462900</v>
       </c>
       <c r="G89" s="3">
-        <v>2807600</v>
+        <v>2695300</v>
       </c>
       <c r="H89" s="3">
-        <v>3078900</v>
+        <v>2955700</v>
       </c>
       <c r="I89" s="3">
-        <v>260700</v>
+        <v>250300</v>
       </c>
       <c r="J89" s="3">
-        <v>734900</v>
+        <v>705500</v>
       </c>
       <c r="K89" s="3">
         <v>936400</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-603000</v>
+        <v>-578900</v>
       </c>
       <c r="E91" s="3">
-        <v>-884700</v>
+        <v>-849300</v>
       </c>
       <c r="F91" s="3">
-        <v>-546500</v>
+        <v>-524600</v>
       </c>
       <c r="G91" s="3">
-        <v>-382500</v>
+        <v>-367200</v>
       </c>
       <c r="H91" s="3">
-        <v>-388900</v>
+        <v>-373300</v>
       </c>
       <c r="I91" s="3">
-        <v>-253500</v>
+        <v>-243400</v>
       </c>
       <c r="J91" s="3">
-        <v>-283000</v>
+        <v>-271700</v>
       </c>
       <c r="K91" s="3">
         <v>-281500</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-39900</v>
+        <v>-38300</v>
       </c>
       <c r="E94" s="3">
-        <v>-1163600</v>
+        <v>-1117100</v>
       </c>
       <c r="F94" s="3">
-        <v>-162600</v>
+        <v>-156100</v>
       </c>
       <c r="G94" s="3">
-        <v>-1880500</v>
+        <v>-1805300</v>
       </c>
       <c r="H94" s="3">
-        <v>-547700</v>
+        <v>-525800</v>
       </c>
       <c r="I94" s="3">
-        <v>-345500</v>
+        <v>-331600</v>
       </c>
       <c r="J94" s="3">
-        <v>-477000</v>
+        <v>-457900</v>
       </c>
       <c r="K94" s="3">
         <v>-267200</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-824500</v>
+        <v>-791600</v>
       </c>
       <c r="E96" s="3">
-        <v>-577700</v>
+        <v>-554600</v>
       </c>
       <c r="F96" s="3">
-        <v>-116800</v>
+        <v>-112100</v>
       </c>
       <c r="G96" s="3">
-        <v>-389000</v>
+        <v>-373400</v>
       </c>
       <c r="H96" s="3">
-        <v>-258100</v>
+        <v>-247800</v>
       </c>
       <c r="I96" s="3">
-        <v>-183900</v>
+        <v>-176600</v>
       </c>
       <c r="J96" s="3">
-        <v>-281600</v>
+        <v>-270300</v>
       </c>
       <c r="K96" s="3">
         <v>-218500</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1357700</v>
+        <v>-1303400</v>
       </c>
       <c r="E100" s="3">
-        <v>213400</v>
+        <v>204800</v>
       </c>
       <c r="F100" s="3">
-        <v>-1702500</v>
+        <v>-1634400</v>
       </c>
       <c r="G100" s="3">
-        <v>-1228900</v>
+        <v>-1179700</v>
       </c>
       <c r="H100" s="3">
-        <v>-1315200</v>
+        <v>-1262600</v>
       </c>
       <c r="I100" s="3">
-        <v>-183200</v>
+        <v>-175900</v>
       </c>
       <c r="J100" s="3">
-        <v>-905200</v>
+        <v>-869000</v>
       </c>
       <c r="K100" s="3">
         <v>-89400</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1352100</v>
+        <v>-1298000</v>
       </c>
       <c r="E101" s="3">
-        <v>888100</v>
+        <v>852500</v>
       </c>
       <c r="F101" s="3">
-        <v>748500</v>
+        <v>718500</v>
       </c>
       <c r="G101" s="3">
-        <v>292600</v>
+        <v>280900</v>
       </c>
       <c r="H101" s="3">
-        <v>35800</v>
+        <v>34400</v>
       </c>
       <c r="I101" s="3">
-        <v>409200</v>
+        <v>392800</v>
       </c>
       <c r="J101" s="3">
-        <v>73700</v>
+        <v>70800</v>
       </c>
       <c r="K101" s="3">
         <v>-149600</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2038600</v>
+        <v>1957000</v>
       </c>
       <c r="E102" s="3">
-        <v>1578900</v>
+        <v>1515700</v>
       </c>
       <c r="F102" s="3">
-        <v>407200</v>
+        <v>390900</v>
       </c>
       <c r="G102" s="3">
-        <v>-9200</v>
+        <v>-8900</v>
       </c>
       <c r="H102" s="3">
-        <v>1251800</v>
+        <v>1201700</v>
       </c>
       <c r="I102" s="3">
-        <v>141300</v>
+        <v>135600</v>
       </c>
       <c r="J102" s="3">
-        <v>-573700</v>
+        <v>-550700</v>
       </c>
       <c r="K102" s="3">
         <v>430200</v>

--- a/AAII_Financials/Yearly/CIB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CIB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>CIB</t>
   </si>
@@ -656,135 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5030700</v>
+        <v>6232900</v>
       </c>
       <c r="E8" s="3">
-        <v>5389300</v>
+        <v>4747200</v>
       </c>
       <c r="F8" s="3">
+        <v>4965400</v>
+      </c>
+      <c r="G8" s="3">
         <v>4206700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3702800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2427000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3842200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3388800</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>229700</v>
+        <v>292100</v>
       </c>
       <c r="E9" s="3">
-        <v>232400</v>
+        <v>216900</v>
       </c>
       <c r="F9" s="3">
+        <v>217400</v>
+      </c>
+      <c r="G9" s="3">
         <v>156400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>145600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>169800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>188700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>180300</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4801000</v>
+        <v>5940800</v>
       </c>
       <c r="E10" s="3">
-        <v>5157000</v>
+        <v>4530300</v>
       </c>
       <c r="F10" s="3">
+        <v>4748000</v>
+      </c>
+      <c r="G10" s="3">
         <v>4050300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3557200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2257200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3653400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3208500</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -796,8 +809,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -822,9 +836,12 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -849,63 +866,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-30100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-47000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-53400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-49500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-20500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-37100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-28800</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>182300</v>
+        <v>213500</v>
       </c>
       <c r="E15" s="3">
-        <v>219100</v>
+        <v>170200</v>
       </c>
       <c r="F15" s="3">
+        <v>205600</v>
+      </c>
+      <c r="G15" s="3">
         <v>152000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>163300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>153400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>150700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>144000</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -914,62 +940,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3091600</v>
+        <v>3674800</v>
       </c>
       <c r="E17" s="3">
-        <v>3339600</v>
+        <v>2868800</v>
       </c>
       <c r="F17" s="3">
+        <v>3077000</v>
+      </c>
+      <c r="G17" s="3">
         <v>2245600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2252400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2338100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2515000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2304200</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1939100</v>
+        <v>2558100</v>
       </c>
       <c r="E18" s="3">
-        <v>2049700</v>
+        <v>1878400</v>
       </c>
       <c r="F18" s="3">
+        <v>1888400</v>
+      </c>
+      <c r="G18" s="3">
         <v>1961100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1450400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>88900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1327200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1084600</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -981,8 +1014,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1007,36 +1041,42 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2121400</v>
+        <v>2771600</v>
       </c>
       <c r="E21" s="3">
-        <v>2268800</v>
+        <v>2048600</v>
       </c>
       <c r="F21" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="G21" s="3">
         <v>2113000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1613700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>242300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1477900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1228600</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1061,63 +1101,72 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1986100</v>
+        <v>2588200</v>
       </c>
       <c r="E23" s="3">
-        <v>2103100</v>
+        <v>1925400</v>
       </c>
       <c r="F23" s="3">
+        <v>1941800</v>
+      </c>
+      <c r="G23" s="3">
         <v>2010600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1470900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>90300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1364300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1113400</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>542500</v>
+        <v>745500</v>
       </c>
       <c r="E24" s="3">
-        <v>498900</v>
+        <v>539700</v>
       </c>
       <c r="F24" s="3">
+        <v>469900</v>
+      </c>
+      <c r="G24" s="3">
         <v>567100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>436600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>384800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>255400</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1142,63 +1191,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1443600</v>
+        <v>1842700</v>
       </c>
       <c r="E26" s="3">
-        <v>1604300</v>
+        <v>1385700</v>
       </c>
       <c r="F26" s="3">
+        <v>1472000</v>
+      </c>
+      <c r="G26" s="3">
         <v>1443500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1034300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>92200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>979500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>858000</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1013200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1421400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1579000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1399600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1004600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>80700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>949900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>818700</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1223,20 +1281,23 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-797400</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>57900</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>132300</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1250,9 +1311,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1277,9 +1341,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1304,9 +1371,12 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1331,36 +1401,42 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1013200</v>
+      </c>
+      <c r="E33" s="3">
         <v>1421400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1579000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1399600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1004600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>80700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>949900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>818700</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1385,68 +1461,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1013200</v>
+      </c>
+      <c r="E35" s="3">
         <v>1421400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1579000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1399600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1004600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>80700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>949900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>818700</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1458,8 +1543,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1471,251 +1557,279 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4370600</v>
+      </c>
+      <c r="E41" s="3">
         <v>4448700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5346000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3955100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3617900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4534900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3785100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3447400</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8942000</v>
+      </c>
+      <c r="E42" s="3">
         <v>7317700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6795800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3924000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4515400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5487200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4055000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3937400</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>450400</v>
+        <v>622400</v>
       </c>
       <c r="E43" s="3">
+        <v>448200</v>
+      </c>
+      <c r="F43" s="3">
         <v>568300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>477700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>464600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>129000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>414600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>222100</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E44" s="3">
         <v>211500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>192900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>105800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>101500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>124800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>120200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>89500</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>799700</v>
+        <v>11057100</v>
       </c>
       <c r="E45" s="3">
+        <v>801900</v>
+      </c>
+      <c r="F45" s="3">
         <v>696200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>518800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>668200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>675200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>542400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>593800</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27852000</v>
+      </c>
+      <c r="E46" s="3">
         <v>15256000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16966400</v>
       </c>
-      <c r="F46" s="3">
-        <v>11081500</v>
-      </c>
       <c r="G46" s="3">
+        <v>11236700</v>
+      </c>
+      <c r="H46" s="3">
         <v>11892600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13363200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11557400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10430200</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3448300</v>
+      </c>
+      <c r="E47" s="3">
         <v>3830800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4243200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4058800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4151300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4801500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3291200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2925200</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1786600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1737900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2105500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1764900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1670600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1743900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1681900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1037300</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>672900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2215100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2191500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2153800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2121000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2195400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2204000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2217700</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1740,9 +1854,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1767,36 +1884,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2016700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1492500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1472000</v>
       </c>
-      <c r="F52" s="3">
-        <v>1079200</v>
-      </c>
       <c r="G52" s="3">
+        <v>924100</v>
+      </c>
+      <c r="H52" s="3">
         <v>972100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1320300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>852300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>684800</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1821,36 +1944,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>100711400</v>
+      </c>
+      <c r="E54" s="3">
         <v>84410200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>88520600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>72793300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>71249000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>74738600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>71936400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>67768000</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1862,8 +1991,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1875,170 +2005,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>71707600</v>
+      </c>
+      <c r="E57" s="3">
         <v>64668900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>65809800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>52452700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>52286700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>53429800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>48771900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>44615700</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2095300</v>
+      </c>
+      <c r="E58" s="3">
         <v>2747100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3068800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3026400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1298000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2472500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3071600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5060800</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>469200</v>
+        <v>9446000</v>
       </c>
       <c r="E59" s="3">
+        <v>342400</v>
+      </c>
+      <c r="F59" s="3">
         <v>614400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>570900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>259600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>266900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>278300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>456500</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>68135800</v>
+        <v>83583800</v>
       </c>
       <c r="E60" s="3">
+        <v>68009000</v>
+      </c>
+      <c r="F60" s="3">
         <v>69785100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>56256400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>54060200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>56263800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>52334000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>50323000</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4233800</v>
+      </c>
+      <c r="E61" s="3">
         <v>4777000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7217900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6604600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7249500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8443900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8955300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7508800</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>546700</v>
+        <v>981100</v>
       </c>
       <c r="E62" s="3">
+        <v>673500</v>
+      </c>
+      <c r="F62" s="3">
         <v>677200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1359700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1111600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1233000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1143000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1075200</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2063,9 +2212,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2090,9 +2242,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2117,36 +2272,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>89839200</v>
+      </c>
+      <c r="E66" s="3">
         <v>74299500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>78440700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>64541000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>62909800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>66516500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>63159300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>59560000</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2158,8 +2319,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2184,9 +2346,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2211,9 +2376,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2238,9 +2406,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2265,36 +2436,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8123900</v>
+      </c>
+      <c r="E72" s="3">
         <v>7156900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7402400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5362800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5413100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5269100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5553300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5021600</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2319,9 +2496,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2346,9 +2526,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2373,36 +2556,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10543000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9874500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9832100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8064900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7923500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7762900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8191600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7651700</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2427,68 +2616,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1013200</v>
+      </c>
+      <c r="E81" s="3">
         <v>1421400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1579000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1399600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1004600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>80700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>949900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>818700</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2500,35 +2698,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>190800</v>
+        <v>208300</v>
       </c>
       <c r="E83" s="3">
-        <v>223600</v>
+        <v>173900</v>
       </c>
       <c r="F83" s="3">
+        <v>203800</v>
+      </c>
+      <c r="G83" s="3">
         <v>159600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>161500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>167500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>161800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>106000</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2553,9 +2755,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2580,9 +2785,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2607,9 +2815,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2634,9 +2845,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2661,36 +2875,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4174400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4057900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>549200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3481700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3118700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2859100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-609900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1584500</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2702,35 +2922,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-595200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-463100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-622600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-730100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-537300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-447500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-473900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-312300</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2755,9 +2979,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2782,36 +3009,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-587700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-126800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-41200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-960300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-159900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2199800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-667500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-425500</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2823,35 +3056,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1219000</v>
+      </c>
+      <c r="E96" s="3">
         <v>770800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>851400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>476700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>114800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>455000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>314600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>226600</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2876,9 +3113,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2903,9 +3143,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2930,88 +3173,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5238400</v>
+      </c>
+      <c r="E100" s="3">
         <v>2060400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2992900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4965700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3067700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4705900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2759600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1680000</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-319800</v>
+      </c>
+      <c r="E101" s="3">
         <v>547000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1396100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>779300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>611200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>342200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>43600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>504000</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>156500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1577400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2104900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1303000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>400300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1525700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>174000</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
